--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 1/СКИМПРОТ ООД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 1/СКИМПРОТ ООД % ГРУПА 1.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="СКИМПРОТ ООД % ГРУПА 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="109">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -70,6 +73,69 @@
     <t>2026-05-14</t>
   </si>
   <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>1185 София Дружба 1</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1117 София Черни Връх</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1192 София, Младост Ал. Малинов</t>
+  </si>
+  <si>
+    <t>1125 Гоце Делчев</t>
+  </si>
+  <si>
+    <t>1131 София Бояна</t>
+  </si>
+  <si>
+    <t>1133 Кресна Е 79</t>
+  </si>
+  <si>
+    <t>1198 Struma Highway</t>
+  </si>
+  <si>
+    <t>1171 Кулата</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
     <t>СВ1514СТ</t>
   </si>
   <si>
@@ -88,6 +154,9 @@
     <t>СВ5349ММ</t>
   </si>
   <si>
+    <t>РА7887КМ</t>
+  </si>
+  <si>
     <t>78970153027721124</t>
   </si>
   <si>
@@ -106,28 +175,154 @@
     <t>78970153027721140</t>
   </si>
   <si>
+    <t>78970153027721173</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>DIESEL DOUBLE FILTER</t>
-  </si>
-  <si>
-    <t>10:46</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>09:26</t>
-  </si>
-  <si>
-    <t>17:39</t>
-  </si>
-  <si>
-    <t>17:21</t>
-  </si>
-  <si>
-    <t>08:37</t>
+    <t>DIESEL DOUBLE FILTERED</t>
+  </si>
+  <si>
+    <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>EKO RACING 100</t>
+  </si>
+  <si>
+    <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:47:00</t>
+  </si>
+  <si>
+    <t>09:04:00</t>
+  </si>
+  <si>
+    <t>09:24:00</t>
+  </si>
+  <si>
+    <t>17:35:00</t>
+  </si>
+  <si>
+    <t>17:19:00</t>
+  </si>
+  <si>
+    <t>08:36:00</t>
+  </si>
+  <si>
+    <t>07:30:00</t>
+  </si>
+  <si>
+    <t>09:16:00</t>
+  </si>
+  <si>
+    <t>09:51:00</t>
+  </si>
+  <si>
+    <t>14:49:00</t>
+  </si>
+  <si>
+    <t>08:20:00</t>
+  </si>
+  <si>
+    <t>16:28:00</t>
+  </si>
+  <si>
+    <t>12:51:00</t>
+  </si>
+  <si>
+    <t>17:29:00</t>
+  </si>
+  <si>
+    <t>15:36:00</t>
+  </si>
+  <si>
+    <t>19:21:00</t>
+  </si>
+  <si>
+    <t>08:51:00</t>
+  </si>
+  <si>
+    <t>08:16:00</t>
+  </si>
+  <si>
+    <t>11:57:00</t>
+  </si>
+  <si>
+    <t>18:17:00</t>
+  </si>
+  <si>
+    <t>13:18:00</t>
+  </si>
+  <si>
+    <t>3231415884 3231415884</t>
+  </si>
+  <si>
+    <t>3231466587 3231466587</t>
+  </si>
+  <si>
+    <t>3231540096 3231540096</t>
+  </si>
+  <si>
+    <t>3231550527 3231550527</t>
+  </si>
+  <si>
+    <t>3231651866 3231651866</t>
+  </si>
+  <si>
+    <t>3231844782 3231844782</t>
+  </si>
+  <si>
+    <t>3232027077 3232027077</t>
+  </si>
+  <si>
+    <t>3232094166 3232094166</t>
+  </si>
+  <si>
+    <t>3232189144 3232189144</t>
+  </si>
+  <si>
+    <t>3232210254 3232210254</t>
+  </si>
+  <si>
+    <t>3232237701 3232237701</t>
+  </si>
+  <si>
+    <t>3232211483 3232211483</t>
+  </si>
+  <si>
+    <t>3232198951 3232198951</t>
+  </si>
+  <si>
+    <t>3232237863 3232237863</t>
+  </si>
+  <si>
+    <t>3232247413 3232247413</t>
+  </si>
+  <si>
+    <t>3232378733 3232378733</t>
+  </si>
+  <si>
+    <t>3232382139 3232382139</t>
+  </si>
+  <si>
+    <t>3232466605 3232466605</t>
+  </si>
+  <si>
+    <t>3232473858 3232473858</t>
+  </si>
+  <si>
+    <t>3232576255 3232576255</t>
+  </si>
+  <si>
+    <t>3232583814 3232583814</t>
+  </si>
+  <si>
+    <t>3232624749 3232624749</t>
   </si>
   <si>
     <t>Общи литри по продукт / СКИМПРОТ ООД % ГРУПА 1</t>
@@ -551,24 +746,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -608,344 +805,1173 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1185</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F2">
         <v>34.4</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2">
         <v>1.43</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>49.19</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.52</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>52.29</v>
       </c>
-      <c r="K2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>143014</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1902</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F3">
         <v>30.35</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3">
         <v>1.43</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>43.4</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.54</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>46.74</v>
       </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>166762</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1101</v>
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F4">
         <v>27.02</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4">
         <v>1.43</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>38.64</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.54</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>41.61</v>
       </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>262581</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>1117</v>
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F5">
         <v>20.23</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5">
         <v>1.43</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>28.93</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.54</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>31.15</v>
       </c>
-      <c r="K5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5">
+      <c r="L5" t="s">
+        <v>63</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="M5">
-        <v>305418</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>1101</v>
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="F6">
         <v>60.61</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6">
+        <v>1.87</v>
+      </c>
+      <c r="I6" s="1">
+        <v>113.34</v>
+      </c>
+      <c r="J6">
         <v>2.06</v>
       </c>
-      <c r="H6">
+      <c r="K6" s="1">
         <v>124.86</v>
       </c>
-      <c r="I6" s="1">
-        <v>2.06</v>
-      </c>
-      <c r="J6">
-        <v>124.86</v>
-      </c>
-      <c r="K6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6">
+      <c r="L6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>263868</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
-        <v>1101</v>
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F7">
         <v>28.92</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7">
         <v>1.47</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>42.51</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.55</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>44.83</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>65</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8">
+        <v>26.68</v>
+      </c>
+      <c r="G8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8">
+        <v>1.48</v>
+      </c>
+      <c r="I8" s="1">
+        <v>39.49</v>
+      </c>
+      <c r="J8">
+        <v>1.55</v>
+      </c>
+      <c r="K8" s="1">
+        <v>41.35</v>
+      </c>
+      <c r="L8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9">
+        <v>28.53</v>
+      </c>
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9">
+        <v>1.49</v>
+      </c>
+      <c r="I9" s="1">
+        <v>42.51</v>
+      </c>
+      <c r="J9">
+        <v>1.54</v>
+      </c>
+      <c r="K9" s="1">
+        <v>43.94</v>
+      </c>
+      <c r="L9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10">
+        <v>17.8</v>
+      </c>
+      <c r="G10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10">
+        <v>1.49</v>
+      </c>
+      <c r="I10" s="1">
+        <v>26.52</v>
+      </c>
+      <c r="J10">
+        <v>1.58</v>
+      </c>
+      <c r="K10" s="1">
+        <v>28.12</v>
+      </c>
+      <c r="L10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10">
+        <v>75409</v>
+      </c>
+      <c r="N10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11">
+        <v>27.76</v>
+      </c>
+      <c r="G11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I11" s="1">
+        <v>22.49</v>
+      </c>
+      <c r="J11">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K11" s="1">
+        <v>22.49</v>
+      </c>
+      <c r="L11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11">
+        <v>75409</v>
+      </c>
+      <c r="N11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12">
+        <v>24.07</v>
+      </c>
+      <c r="G12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12">
+        <v>1.49</v>
+      </c>
+      <c r="I12" s="1">
+        <v>35.86</v>
+      </c>
+      <c r="J12">
+        <v>1.57</v>
+      </c>
+      <c r="K12" s="1">
+        <v>37.79</v>
+      </c>
+      <c r="L12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13">
+        <v>20.82</v>
+      </c>
+      <c r="G13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13">
+        <v>1.49</v>
+      </c>
+      <c r="I13" s="1">
+        <v>31.02</v>
+      </c>
+      <c r="J13">
+        <v>1.57</v>
+      </c>
+      <c r="K13" s="1">
+        <v>32.69</v>
+      </c>
+      <c r="L13" t="s">
+        <v>69</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14">
+        <v>8.91</v>
+      </c>
+      <c r="G14" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14">
+        <v>1.49</v>
+      </c>
+      <c r="I14" s="1">
+        <v>13.28</v>
+      </c>
+      <c r="J14">
+        <v>1.57</v>
+      </c>
+      <c r="K14" s="1">
+        <v>13.99</v>
+      </c>
+      <c r="L14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M14">
+        <v>70800</v>
+      </c>
+      <c r="N14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
         <v>37</v>
       </c>
-      <c r="L7">
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15">
+        <v>36.3</v>
+      </c>
+      <c r="G15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15">
+        <v>1.87</v>
+      </c>
+      <c r="I15" s="1">
+        <v>67.88</v>
+      </c>
+      <c r="J15">
+        <v>2.01</v>
+      </c>
+      <c r="K15" s="1">
+        <v>72.95999999999999</v>
+      </c>
+      <c r="L15" t="s">
+        <v>71</v>
+      </c>
+      <c r="M15">
         <v>0</v>
       </c>
-      <c r="M7">
-        <v>155243</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="3" t="s">
+      <c r="N15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16">
+        <v>33.88</v>
+      </c>
+      <c r="G16" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16">
+        <v>1.78</v>
+      </c>
+      <c r="I16" s="1">
+        <v>60.31</v>
+      </c>
+      <c r="J16">
+        <v>1.83</v>
+      </c>
+      <c r="K16" s="1">
+        <v>62</v>
+      </c>
+      <c r="L16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17">
+        <v>10.12</v>
+      </c>
+      <c r="G17" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17">
+        <v>1.49</v>
+      </c>
+      <c r="I17" s="1">
+        <v>15.08</v>
+      </c>
+      <c r="J17">
+        <v>1.58</v>
+      </c>
+      <c r="K17" s="1">
+        <v>15.99</v>
+      </c>
+      <c r="L17" t="s">
+        <v>73</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18">
+        <v>27.74</v>
+      </c>
+      <c r="G18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18">
+        <v>1.49</v>
+      </c>
+      <c r="I18" s="1">
+        <v>41.33</v>
+      </c>
+      <c r="J18">
+        <v>1.57</v>
+      </c>
+      <c r="K18" s="1">
+        <v>43.55</v>
+      </c>
+      <c r="L18" t="s">
+        <v>74</v>
+      </c>
+      <c r="M18">
+        <v>71300</v>
+      </c>
+      <c r="N18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19">
+        <v>27.44</v>
+      </c>
+      <c r="G19" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19">
+        <v>1.49</v>
+      </c>
+      <c r="I19" s="1">
+        <v>40.89</v>
+      </c>
+      <c r="J19">
+        <v>1.58</v>
+      </c>
+      <c r="K19" s="1">
+        <v>43.36</v>
+      </c>
+      <c r="L19" t="s">
+        <v>75</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C20" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20">
+        <v>35.12</v>
+      </c>
+      <c r="G20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20">
+        <v>1.49</v>
+      </c>
+      <c r="I20" s="1">
+        <v>52.33</v>
+      </c>
+      <c r="J20">
+        <v>1.57</v>
+      </c>
+      <c r="K20" s="1">
+        <v>55.14</v>
+      </c>
+      <c r="L20" t="s">
+        <v>76</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21">
+        <v>28.8</v>
+      </c>
+      <c r="G21" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21">
+        <v>1.49</v>
+      </c>
+      <c r="I21" s="1">
+        <v>42.91</v>
+      </c>
+      <c r="J21">
+        <v>1.58</v>
+      </c>
+      <c r="K21" s="1">
+        <v>45.5</v>
+      </c>
+      <c r="L21" t="s">
+        <v>77</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22">
+        <v>22.23</v>
+      </c>
+      <c r="G22" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22">
+        <v>1.51</v>
+      </c>
+      <c r="I22" s="1">
+        <v>33.57</v>
+      </c>
+      <c r="J22">
+        <v>1.58</v>
+      </c>
+      <c r="K22" s="1">
+        <v>35.12</v>
+      </c>
+      <c r="L22" t="s">
+        <v>78</v>
+      </c>
+      <c r="M22">
+        <v>71800</v>
+      </c>
+      <c r="N22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="6">
-        <v>140.92</v>
-      </c>
-      <c r="C12" s="6">
-        <v>5</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.4382</v>
-      </c>
-      <c r="E12" s="6">
-        <v>202.67</v>
-      </c>
-      <c r="F12" s="6">
-        <v>216.62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="6">
-        <v>60.61</v>
-      </c>
-      <c r="C13" s="6">
+      <c r="D23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23">
+        <v>20.69</v>
+      </c>
+      <c r="G23" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23">
+        <v>1.51</v>
+      </c>
+      <c r="I23" s="1">
+        <v>31.24</v>
+      </c>
+      <c r="J23">
+        <v>1.57</v>
+      </c>
+      <c r="K23" s="1">
+        <v>32.48</v>
+      </c>
+      <c r="L23" t="s">
+        <v>79</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24">
+        <v>29.25</v>
+      </c>
+      <c r="G24" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24">
+        <v>1.62</v>
+      </c>
+      <c r="I24" s="1">
+        <v>47.39</v>
+      </c>
+      <c r="J24">
+        <v>1.71</v>
+      </c>
+      <c r="K24" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="L24" t="s">
+        <v>80</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="6">
+        <v>439.87</v>
+      </c>
+      <c r="C29" s="6">
+        <v>18</v>
+      </c>
+      <c r="D29" s="7">
+        <v>1.4748</v>
+      </c>
+      <c r="E29" s="6">
+        <v>648.7</v>
+      </c>
+      <c r="F29" s="6">
+        <v>685.64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="6">
+        <v>96.91</v>
+      </c>
+      <c r="C30" s="6">
+        <v>2</v>
+      </c>
+      <c r="D30" s="7">
+        <v>1.87</v>
+      </c>
+      <c r="E30" s="6">
+        <v>181.22</v>
+      </c>
+      <c r="F30" s="6">
+        <v>197.82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="6">
+        <v>33.88</v>
+      </c>
+      <c r="C31" s="6">
         <v>1</v>
       </c>
-      <c r="D13" s="7">
-        <v>2.0601</v>
-      </c>
-      <c r="E13" s="6">
-        <v>124.86</v>
-      </c>
-      <c r="F13" s="6">
-        <v>124.86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="9">
-        <v>201.53</v>
-      </c>
-      <c r="C14" s="9">
-        <v>6</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="9">
-        <v>327.53</v>
-      </c>
-      <c r="F14" s="9">
-        <v>341.48</v>
+      <c r="D31" s="7">
+        <v>1.7801</v>
+      </c>
+      <c r="E31" s="6">
+        <v>60.31</v>
+      </c>
+      <c r="F31" s="6">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="6">
+        <v>29.25</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7">
+        <v>1.6202</v>
+      </c>
+      <c r="E32" s="6">
+        <v>47.39</v>
+      </c>
+      <c r="F32" s="6">
+        <v>50.02</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="6">
+        <v>27.76</v>
+      </c>
+      <c r="C33" s="6">
+        <v>1</v>
+      </c>
+      <c r="D33" s="7">
+        <v>0.8102</v>
+      </c>
+      <c r="E33" s="6">
+        <v>22.49</v>
+      </c>
+      <c r="F33" s="6">
+        <v>22.49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="9">
+        <v>627.67</v>
+      </c>
+      <c r="C34" s="9">
+        <v>23</v>
+      </c>
+      <c r="D34" s="7"/>
+      <c r="E34" s="9">
+        <v>960.11</v>
+      </c>
+      <c r="F34" s="9">
+        <v>1017.97</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 1/СКИМПРОТ ООД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 1/СКИМПРОТ ООД % ГРУПА 1.xlsx
@@ -376,7 +376,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -386,12 +386,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,17 +435,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 1/СКИМПРОТ ООД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 1/СКИМПРОТ ООД % ГРУПА 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="77">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-03</t>
   </si>
   <si>
@@ -73,22 +82,25 @@
     <t>2026-06-19</t>
   </si>
   <si>
-    <t>Ихтиман</t>
-  </si>
-  <si>
-    <t>Кулата</t>
-  </si>
-  <si>
-    <t>София Младост</t>
-  </si>
-  <si>
-    <t>София Малинова Долина</t>
-  </si>
-  <si>
-    <t>София Дружба 2</t>
-  </si>
-  <si>
-    <t>Тракия</t>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1171 Кулата</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1157 Пловдив Тракия</t>
   </si>
   <si>
     <t>СВ8630СК</t>
@@ -142,40 +154,79 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-06-03 12:38:00</t>
-  </si>
-  <si>
-    <t>2026-06-03 14:45:38</t>
-  </si>
-  <si>
-    <t>2026-06-06 09:39:20</t>
-  </si>
-  <si>
-    <t>2026-06-10 11:50:32</t>
-  </si>
-  <si>
-    <t>2026-06-11 11:20:24</t>
-  </si>
-  <si>
-    <t>2026-06-11 20:28:20</t>
-  </si>
-  <si>
-    <t>2026-06-12 17:10:39</t>
-  </si>
-  <si>
-    <t>2026-06-16 16:31:31</t>
-  </si>
-  <si>
-    <t>2026-06-17 09:48:31</t>
-  </si>
-  <si>
-    <t>2026-06-19 11:40:48</t>
-  </si>
-  <si>
-    <t>2026-06-19 15:09:23</t>
-  </si>
-  <si>
-    <t>2026-06-19 15:09:24</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>12:37:00</t>
+  </si>
+  <si>
+    <t>14:45:00</t>
+  </si>
+  <si>
+    <t>09:36:00</t>
+  </si>
+  <si>
+    <t>11:50:00</t>
+  </si>
+  <si>
+    <t>11:19:00</t>
+  </si>
+  <si>
+    <t>20:28:00</t>
+  </si>
+  <si>
+    <t>17:08:00</t>
+  </si>
+  <si>
+    <t>16:28:00</t>
+  </si>
+  <si>
+    <t>09:43:00</t>
+  </si>
+  <si>
+    <t>15:07:00</t>
+  </si>
+  <si>
+    <t>11:40:00</t>
+  </si>
+  <si>
+    <t>19:42:00</t>
+  </si>
+  <si>
+    <t>3232804209 3232804209</t>
+  </si>
+  <si>
+    <t>3232818901 3232818901</t>
+  </si>
+  <si>
+    <t>3232933990 3232933990</t>
+  </si>
+  <si>
+    <t>3233135559 3233135559</t>
+  </si>
+  <si>
+    <t>3233189819 3233189819</t>
+  </si>
+  <si>
+    <t>3233206106 3233206106</t>
+  </si>
+  <si>
+    <t>3233246743 3233246743</t>
+  </si>
+  <si>
+    <t>3233433471 3233433471</t>
+  </si>
+  <si>
+    <t>3233481230 3233481230</t>
+  </si>
+  <si>
+    <t>3233578333 3233578333</t>
+  </si>
+  <si>
+    <t>3233574367 3233574367</t>
+  </si>
+  <si>
+    <t>3233910794 3233910794</t>
   </si>
   <si>
     <t>Общи литри по продукт / СКИМПРОТ ООД % ГРУПА 1</t>
@@ -593,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -602,14 +653,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -643,538 +697,699 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F2">
         <v>28.53</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2">
         <v>1.51</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>43.08</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.58</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>45.08</v>
       </c>
-      <c r="K2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F3">
         <v>21.97</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3">
         <v>1.51</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>33.17</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.58</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>34.71</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3">
+        <v>72100</v>
+      </c>
+      <c r="N3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>39</v>
       </c>
       <c r="F4">
         <v>33.22</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4">
         <v>1.49</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>49.5</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.56</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>51.82</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>49</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" t="s">
-        <v>40</v>
       </c>
       <c r="F5">
         <v>59.49</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5">
         <v>1.8</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>107.08</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.9</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>113.03</v>
       </c>
-      <c r="K5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>50</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F6">
         <v>24.66</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6">
         <v>1.47</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>36.25</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.57</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>38.72</v>
       </c>
-      <c r="K6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F7">
         <v>31.47</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7">
         <v>1.47</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>46.26</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.56</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>49.09</v>
       </c>
-      <c r="K7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F8">
         <v>33.85</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8">
         <v>1.47</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>49.76</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.56</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>52.81</v>
       </c>
-      <c r="K8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F9">
         <v>34.12</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9">
         <v>1.47</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>50.16</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.56</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>53.23</v>
       </c>
-      <c r="K9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F10">
         <v>19.25</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10">
         <v>1.45</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>27.91</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.56</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>30.03</v>
       </c>
-      <c r="K10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F11">
-        <v>24</v>
-      </c>
-      <c r="G11" s="1">
+        <v>14.95</v>
+      </c>
+      <c r="G11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11">
         <v>1.45</v>
       </c>
-      <c r="H11">
-        <v>34.8</v>
-      </c>
       <c r="I11" s="1">
-        <v>1.54</v>
+        <v>21.68</v>
       </c>
       <c r="J11">
-        <v>36.96</v>
-      </c>
-      <c r="K11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>1.55</v>
+      </c>
+      <c r="K11" s="1">
+        <v>23.17</v>
+      </c>
+      <c r="L11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F12">
         <v>27.3</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12">
         <v>0.66</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>18.02</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>0.66</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>18.02</v>
       </c>
-      <c r="K12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13">
+        <v>24</v>
+      </c>
+      <c r="G13" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13">
+        <v>1.45</v>
+      </c>
+      <c r="I13" s="1">
+        <v>34.8</v>
+      </c>
+      <c r="J13">
+        <v>1.54</v>
+      </c>
+      <c r="K13" s="1">
+        <v>36.96</v>
+      </c>
+      <c r="L13" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
         <v>31</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13">
-        <v>14.95</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1.45</v>
-      </c>
-      <c r="H13">
-        <v>21.68</v>
-      </c>
-      <c r="I13" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J13">
-        <v>23.17</v>
-      </c>
-      <c r="K13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14">
+        <v>29.11</v>
+      </c>
+      <c r="G14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14">
+        <v>1.4</v>
+      </c>
+      <c r="I14" s="1">
+        <v>40.75</v>
+      </c>
+      <c r="J14">
+        <v>1.5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>43.66</v>
+      </c>
+      <c r="L14" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="6">
-        <v>266.02</v>
-      </c>
-      <c r="C18" s="6">
+      <c r="A18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="D18" s="7">
-        <v>1.4757</v>
-      </c>
-      <c r="E18" s="6">
-        <v>392.57</v>
-      </c>
-      <c r="F18" s="6">
-        <v>415.62</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B19" s="6">
-        <v>59.49</v>
+        <v>295.13</v>
       </c>
       <c r="C19" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D19" s="7">
-        <v>1.8</v>
+        <v>1.4682</v>
       </c>
       <c r="E19" s="6">
-        <v>107.08</v>
+        <v>433.32</v>
       </c>
       <c r="F19" s="6">
-        <v>113.03</v>
+        <v>459.28</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B20" s="6">
-        <v>27.3</v>
+        <v>59.49</v>
       </c>
       <c r="C20" s="6">
         <v>1</v>
       </c>
       <c r="D20" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="E20" s="6">
+        <v>107.08</v>
+      </c>
+      <c r="F20" s="6">
+        <v>113.03</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="6">
+        <v>27.3</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1</v>
+      </c>
+      <c r="D21" s="7">
         <v>0.6601</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E21" s="6">
         <v>18.02</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F21" s="6">
         <v>18.02</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="9">
-        <v>352.81</v>
-      </c>
-      <c r="C21" s="9">
-        <v>12</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="9">
-        <v>517.67</v>
-      </c>
-      <c r="F21" s="9">
-        <v>546.67</v>
+    <row r="22" spans="1:6">
+      <c r="A22" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="9">
+        <v>381.92</v>
+      </c>
+      <c r="C22" s="9">
+        <v>13</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="9">
+        <v>558.42</v>
+      </c>
+      <c r="F22" s="9">
+        <v>590.33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 1/СКИМПРОТ ООД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 1/СКИМПРОТ ООД % ГРУПА 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="93">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-01</t>
   </si>
   <si>
@@ -73,22 +79,52 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>Ихтиман</t>
-  </si>
-  <si>
-    <t>София Черни връх</t>
-  </si>
-  <si>
-    <t>Кулата Струма</t>
-  </si>
-  <si>
-    <t>Монтана</t>
-  </si>
-  <si>
-    <t>София Дружба 2</t>
-  </si>
-  <si>
-    <t>София Вапцаров</t>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>1101 София Ихтиман</t>
+  </si>
+  <si>
+    <t>1117 София Черни Връх</t>
+  </si>
+  <si>
+    <t>1198 Struma Highway</t>
+  </si>
+  <si>
+    <t>1134 Монтана</t>
+  </si>
+  <si>
+    <t>1145 София Вапцаров</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1171 Кулата</t>
+  </si>
+  <si>
+    <t>1120 Пловдив Радиново</t>
+  </si>
+  <si>
+    <t>1902 София, О5 Малинова Долина</t>
   </si>
   <si>
     <t>СВ8630СК</t>
@@ -133,37 +169,112 @@
     <t>EKO RACING 100</t>
   </si>
   <si>
-    <t>2026-07-01 09:52:55</t>
-  </si>
-  <si>
-    <t>2026-07-01 11:28:46</t>
-  </si>
-  <si>
-    <t>2026-07-02 17:43:36</t>
-  </si>
-  <si>
-    <t>2026-07-07 09:39:46</t>
-  </si>
-  <si>
-    <t>2026-07-07 12:40:29</t>
-  </si>
-  <si>
-    <t>2026-07-08 16:35:45</t>
-  </si>
-  <si>
-    <t>2026-07-09 06:48:00</t>
-  </si>
-  <si>
-    <t>2026-07-10 10:35:48</t>
-  </si>
-  <si>
-    <t>2026-07-15 09:32:52</t>
-  </si>
-  <si>
-    <t>2026-07-15 20:19:53</t>
-  </si>
-  <si>
-    <t>2026-07-15 21:49:26</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>09:52:00</t>
+  </si>
+  <si>
+    <t>11:28:00</t>
+  </si>
+  <si>
+    <t>17:36:00</t>
+  </si>
+  <si>
+    <t>09:39:00</t>
+  </si>
+  <si>
+    <t>12:39:00</t>
+  </si>
+  <si>
+    <t>16:36:00</t>
+  </si>
+  <si>
+    <t>06:47:00</t>
+  </si>
+  <si>
+    <t>10:35:00</t>
+  </si>
+  <si>
+    <t>09:32:00</t>
+  </si>
+  <si>
+    <t>21:51:00</t>
+  </si>
+  <si>
+    <t>20:20:00</t>
+  </si>
+  <si>
+    <t>11:03:00</t>
+  </si>
+  <si>
+    <t>10:20:00</t>
+  </si>
+  <si>
+    <t>13:25:00</t>
+  </si>
+  <si>
+    <t>20:47:00</t>
+  </si>
+  <si>
+    <t>16:08:00</t>
+  </si>
+  <si>
+    <t>09:21:00</t>
+  </si>
+  <si>
+    <t>3234149723 3234149723</t>
+  </si>
+  <si>
+    <t>3234152034 3234152034</t>
+  </si>
+  <si>
+    <t>3234169467 3234169467</t>
+  </si>
+  <si>
+    <t>3234436601 3234436601</t>
+  </si>
+  <si>
+    <t>3234437944 3234437944</t>
+  </si>
+  <si>
+    <t>3234482835 3234482835</t>
+  </si>
+  <si>
+    <t>3234500119 3234500119</t>
+  </si>
+  <si>
+    <t>3234608374 3234608374</t>
+  </si>
+  <si>
+    <t>3234830257 3234830257</t>
+  </si>
+  <si>
+    <t>3234844794 3234844794</t>
+  </si>
+  <si>
+    <t>3234846532 3234846532</t>
+  </si>
+  <si>
+    <t>3235088248 3235088248</t>
+  </si>
+  <si>
+    <t>3235134419 3235134419</t>
+  </si>
+  <si>
+    <t>3235243637 3235243637</t>
+  </si>
+  <si>
+    <t>3235249833 3235249833</t>
+  </si>
+  <si>
+    <t>3235346193 3235346193</t>
+  </si>
+  <si>
+    <t>3235438236 3235438236</t>
+  </si>
+  <si>
+    <t>3235508070 3235508070</t>
   </si>
   <si>
     <t>Общи литри по продукт / СКИМПРОТ ООД % ГРУПА 1</t>
@@ -581,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -590,15 +701,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -635,556 +748,936 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F2">
         <v>26.92</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2">
         <v>1.39</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>37.42</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.51</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>40.65</v>
       </c>
-      <c r="K2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="L2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F3">
         <v>36</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3">
         <v>1.39</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>50.04</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.51</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>54.36</v>
       </c>
-      <c r="K3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="L3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F4">
         <v>21.55</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4">
         <v>1.39</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>29.95</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.5</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>32.33</v>
       </c>
-      <c r="K4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="L4" t="s">
+        <v>54</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F5">
         <v>22.79</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5">
         <v>1.39</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>31.68</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.52</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>34.64</v>
       </c>
-      <c r="K5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="L5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F6">
         <v>52.13</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6">
         <v>1.44</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>75.06999999999999</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.55</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>80.8</v>
       </c>
-      <c r="K6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="L6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F7">
         <v>17.59</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7">
         <v>1.68</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>29.55</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.82</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>32.01</v>
       </c>
-      <c r="K7" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="L7" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F8">
         <v>46.15</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8">
         <v>1.39</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>64.15000000000001</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.49</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>68.76000000000001</v>
       </c>
-      <c r="K8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="L8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F9">
         <v>21.24</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9">
         <v>1.39</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>29.52</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.52</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>32.28</v>
       </c>
-      <c r="K9" t="s">
-        <v>46</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="L9" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F10">
         <v>26</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10">
         <v>1.4</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>36.4</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.51</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>39.26</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>43.14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11">
+        <v>1.69</v>
+      </c>
+      <c r="I11" s="1">
+        <v>72.91</v>
+      </c>
+      <c r="J11">
+        <v>1.76</v>
+      </c>
+      <c r="K11" s="1">
+        <v>75.93000000000001</v>
+      </c>
+      <c r="L11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
         <v>47</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
+      <c r="F12">
+        <v>30.31</v>
+      </c>
+      <c r="G12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12">
+        <v>1.4</v>
+      </c>
+      <c r="I12" s="1">
+        <v>42.43</v>
+      </c>
+      <c r="J12">
+        <v>1.49</v>
+      </c>
+      <c r="K12" s="1">
+        <v>45.16</v>
+      </c>
+      <c r="L12" t="s">
+        <v>62</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13">
+        <v>1.42</v>
+      </c>
+      <c r="I13" s="1">
+        <v>49.7</v>
+      </c>
+      <c r="J13">
+        <v>1.55</v>
+      </c>
+      <c r="K13" s="1">
+        <v>54.25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14">
+        <v>29.35</v>
+      </c>
+      <c r="G14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14">
+        <v>1.42</v>
+      </c>
+      <c r="I14" s="1">
+        <v>41.68</v>
+      </c>
+      <c r="J14">
+        <v>1.55</v>
+      </c>
+      <c r="K14" s="1">
+        <v>45.49</v>
+      </c>
+      <c r="L14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15">
+        <v>43.46</v>
+      </c>
+      <c r="G15" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15">
+        <v>1.73</v>
+      </c>
+      <c r="I15" s="1">
+        <v>75.19</v>
+      </c>
+      <c r="J15">
+        <v>1.99</v>
+      </c>
+      <c r="K15" s="1">
+        <v>86.48999999999999</v>
+      </c>
+      <c r="L15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16">
+        <v>25.58</v>
+      </c>
+      <c r="G16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16">
+        <v>1.43</v>
+      </c>
+      <c r="I16" s="1">
+        <v>36.58</v>
+      </c>
+      <c r="J16">
+        <v>1.54</v>
+      </c>
+      <c r="K16" s="1">
+        <v>39.39</v>
+      </c>
+      <c r="L16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17">
+        <v>31.25</v>
+      </c>
+      <c r="G17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17">
+        <v>1.43</v>
+      </c>
+      <c r="I17" s="1">
+        <v>44.69</v>
+      </c>
+      <c r="J17">
+        <v>1.58</v>
+      </c>
+      <c r="K17" s="1">
+        <v>49.38</v>
+      </c>
+      <c r="L17" t="s">
+        <v>67</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18">
+        <v>15.02</v>
+      </c>
+      <c r="G18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18">
+        <v>1.43</v>
+      </c>
+      <c r="I18" s="1">
+        <v>21.48</v>
+      </c>
+      <c r="J18">
+        <v>1.56</v>
+      </c>
+      <c r="K18" s="1">
+        <v>23.43</v>
+      </c>
+      <c r="L18" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18">
+        <v>73500</v>
+      </c>
+      <c r="N18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19">
+        <v>30.17</v>
+      </c>
+      <c r="G19" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19">
+        <v>1.48</v>
+      </c>
+      <c r="I19" s="1">
+        <v>44.65</v>
+      </c>
+      <c r="J19">
+        <v>1.56</v>
+      </c>
+      <c r="K19" s="1">
+        <v>47.07</v>
+      </c>
+      <c r="L19" t="s">
+        <v>68</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="6">
+        <v>397.33</v>
+      </c>
+      <c r="C24" s="6">
+        <v>14</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1.4103</v>
+      </c>
+      <c r="E24" s="6">
+        <v>560.37</v>
+      </c>
+      <c r="F24" s="6">
+        <v>606.45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="6">
+        <v>61.05</v>
+      </c>
+      <c r="C25" s="6">
+        <v>2</v>
+      </c>
+      <c r="D25" s="7">
+        <v>1.7156</v>
+      </c>
+      <c r="E25" s="6">
+        <v>104.74</v>
+      </c>
+      <c r="F25" s="6">
+        <v>118.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="6">
+        <v>52.13</v>
+      </c>
+      <c r="C26" s="6">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7">
+        <v>1.4401</v>
+      </c>
+      <c r="E26" s="6">
+        <v>75.06999999999999</v>
+      </c>
+      <c r="F26" s="6">
+        <v>80.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="6">
+        <v>43.14</v>
+      </c>
+      <c r="C27" s="6">
+        <v>1</v>
+      </c>
+      <c r="D27" s="7">
+        <v>1.6901</v>
+      </c>
+      <c r="E27" s="6">
+        <v>72.91</v>
+      </c>
+      <c r="F27" s="6">
+        <v>75.93000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="9">
+        <v>553.65</v>
+      </c>
+      <c r="C28" s="9">
         <v>18</v>
       </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11">
-        <v>30.31</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="H11">
-        <v>42.43</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="J11">
-        <v>45.16</v>
-      </c>
-      <c r="K11" t="s">
-        <v>48</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12">
-        <v>43.14</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="H12">
-        <v>72.91</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="J12">
-        <v>75.93000000000001</v>
-      </c>
-      <c r="K12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="6">
-        <v>230.96</v>
-      </c>
-      <c r="C17" s="6">
-        <v>8</v>
-      </c>
-      <c r="D17" s="7">
-        <v>1.3924</v>
-      </c>
-      <c r="E17" s="6">
-        <v>321.59</v>
-      </c>
-      <c r="F17" s="6">
-        <v>347.44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="6">
-        <v>52.13</v>
-      </c>
-      <c r="C18" s="6">
-        <v>1</v>
-      </c>
-      <c r="D18" s="7">
-        <v>1.4401</v>
-      </c>
-      <c r="E18" s="6">
-        <v>75.06999999999999</v>
-      </c>
-      <c r="F18" s="6">
-        <v>80.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="6">
-        <v>43.14</v>
-      </c>
-      <c r="C19" s="6">
-        <v>1</v>
-      </c>
-      <c r="D19" s="7">
-        <v>1.6901</v>
-      </c>
-      <c r="E19" s="6">
-        <v>72.91</v>
-      </c>
-      <c r="F19" s="6">
-        <v>75.93000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="6">
-        <v>17.59</v>
-      </c>
-      <c r="C20" s="6">
-        <v>1</v>
-      </c>
-      <c r="D20" s="7">
-        <v>1.6799</v>
-      </c>
-      <c r="E20" s="6">
-        <v>29.55</v>
-      </c>
-      <c r="F20" s="6">
-        <v>32.01</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="9">
-        <v>343.82</v>
-      </c>
-      <c r="C21" s="9">
-        <v>11</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="9">
-        <v>499.12</v>
-      </c>
-      <c r="F21" s="9">
-        <v>536.1799999999999</v>
+      <c r="D28" s="7"/>
+      <c r="E28" s="9">
+        <v>813.09</v>
+      </c>
+      <c r="F28" s="9">
+        <v>881.6799999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A22:F22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 1/СКИМПРОТ ООД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 1/СКИМПРОТ ООД % ГРУПА 1.xlsx
@@ -301,7 +301,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1588,7 +1588,7 @@
         <v>14</v>
       </c>
       <c r="D24" s="7">
-        <v>1.4103</v>
+        <v>1.410339</v>
       </c>
       <c r="E24" s="6">
         <v>560.37</v>
@@ -1608,7 +1608,7 @@
         <v>2</v>
       </c>
       <c r="D25" s="7">
-        <v>1.7156</v>
+        <v>1.715643</v>
       </c>
       <c r="E25" s="6">
         <v>104.74</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="7">
-        <v>1.4401</v>
+        <v>1.440054</v>
       </c>
       <c r="E26" s="6">
         <v>75.06999999999999</v>
@@ -1648,7 +1648,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="7">
-        <v>1.6901</v>
+        <v>1.690079</v>
       </c>
       <c r="E27" s="6">
         <v>72.91</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 1/СКИМПРОТ ООД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 1/СКИМПРОТ ООД % ГРУПА 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="94">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -692,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -705,13 +708,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -754,802 +757,859 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2">
-        <v>26.92</v>
+        <v>26.921</v>
       </c>
       <c r="G2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H2">
-        <v>1.39</v>
+        <v>1.359</v>
       </c>
       <c r="I2" s="1">
-        <v>37.42</v>
+        <v>1.389</v>
       </c>
       <c r="J2">
+        <v>37.393269</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.51</v>
       </c>
-      <c r="K2" s="1">
-        <v>40.65</v>
-      </c>
-      <c r="L2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>40.65071</v>
+      </c>
+      <c r="M2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3">
         <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H3">
-        <v>1.39</v>
+        <v>1.359</v>
       </c>
       <c r="I3" s="1">
-        <v>50.04</v>
+        <v>1.389</v>
       </c>
       <c r="J3">
+        <v>50.004</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.51</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>54.36</v>
       </c>
-      <c r="L3" t="s">
-        <v>53</v>
-      </c>
-      <c r="M3">
+      <c r="M3" t="s">
+        <v>54</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4">
+        <v>21.553</v>
+      </c>
+      <c r="G4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4">
+        <v>1.359</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.389</v>
+      </c>
+      <c r="J4">
+        <v>29.937117</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="L4" s="1">
+        <v>32.3295</v>
+      </c>
+      <c r="M4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5">
+        <v>22.789</v>
+      </c>
+      <c r="G5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5">
+        <v>1.359</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.389</v>
+      </c>
+      <c r="J5">
+        <v>31.653921</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L5" s="1">
+        <v>34.63928</v>
+      </c>
+      <c r="M5" t="s">
+        <v>56</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6">
+        <v>52.129</v>
+      </c>
+      <c r="G6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6">
+        <v>1.406</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.436</v>
+      </c>
+      <c r="J6">
+        <v>74.85724399999999</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L6" s="1">
+        <v>80.79995</v>
+      </c>
+      <c r="M6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>17.588</v>
+      </c>
+      <c r="G7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7">
+        <v>1.599</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.679</v>
+      </c>
+      <c r="J7">
+        <v>29.530252</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.82</v>
+      </c>
+      <c r="L7" s="1">
+        <v>32.01016</v>
+      </c>
+      <c r="M7" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
         <v>39</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D8" t="s">
         <v>44</v>
       </c>
-      <c r="E4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4">
-        <v>21.55</v>
-      </c>
-      <c r="G4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4">
-        <v>1.39</v>
-      </c>
-      <c r="I4" s="1">
-        <v>29.95</v>
-      </c>
-      <c r="J4">
-        <v>1.5</v>
-      </c>
-      <c r="K4" s="1">
-        <v>32.33</v>
-      </c>
-      <c r="L4" t="s">
-        <v>54</v>
-      </c>
-      <c r="M4">
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8">
+        <v>46.148</v>
+      </c>
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <v>1.359</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.389</v>
+      </c>
+      <c r="J8">
+        <v>64.09957199999999</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L8" s="1">
+        <v>68.76052</v>
+      </c>
+      <c r="M8" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5">
-        <v>22.79</v>
-      </c>
-      <c r="G5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5">
-        <v>1.39</v>
-      </c>
-      <c r="I5" s="1">
-        <v>31.68</v>
-      </c>
-      <c r="J5">
+      <c r="O8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9">
+        <v>21.237</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9">
+        <v>1.359</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.389</v>
+      </c>
+      <c r="J9">
+        <v>29.498193</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.52</v>
       </c>
-      <c r="K5" s="1">
-        <v>34.64</v>
-      </c>
-      <c r="L5" t="s">
-        <v>55</v>
-      </c>
-      <c r="M5">
+      <c r="L9" s="1">
+        <v>32.28024</v>
+      </c>
+      <c r="M9" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="O9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" t="s">
         <v>48</v>
-      </c>
-      <c r="F6">
-        <v>52.13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6">
-        <v>1.44</v>
-      </c>
-      <c r="I6" s="1">
-        <v>75.06999999999999</v>
-      </c>
-      <c r="J6">
-        <v>1.55</v>
-      </c>
-      <c r="K6" s="1">
-        <v>80.8</v>
-      </c>
-      <c r="L6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7">
-        <v>17.59</v>
-      </c>
-      <c r="G7" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7">
-        <v>1.68</v>
-      </c>
-      <c r="I7" s="1">
-        <v>29.55</v>
-      </c>
-      <c r="J7">
-        <v>1.82</v>
-      </c>
-      <c r="K7" s="1">
-        <v>32.01</v>
-      </c>
-      <c r="L7" t="s">
-        <v>57</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8">
-        <v>46.15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>51</v>
-      </c>
-      <c r="H8">
-        <v>1.39</v>
-      </c>
-      <c r="I8" s="1">
-        <v>64.15000000000001</v>
-      </c>
-      <c r="J8">
-        <v>1.49</v>
-      </c>
-      <c r="K8" s="1">
-        <v>68.76000000000001</v>
-      </c>
-      <c r="L8" t="s">
-        <v>58</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9">
-        <v>21.24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9">
-        <v>1.39</v>
-      </c>
-      <c r="I9" s="1">
-        <v>29.52</v>
-      </c>
-      <c r="J9">
-        <v>1.52</v>
-      </c>
-      <c r="K9" s="1">
-        <v>32.28</v>
-      </c>
-      <c r="L9" t="s">
-        <v>59</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" t="s">
-        <v>47</v>
       </c>
       <c r="F10">
         <v>26</v>
       </c>
       <c r="G10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10">
+        <v>1.369</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.399</v>
+      </c>
+      <c r="J10">
+        <v>36.374</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="L10" s="1">
+        <v>39.26</v>
+      </c>
+      <c r="M10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
         <v>51</v>
       </c>
-      <c r="H10">
-        <v>1.4</v>
-      </c>
-      <c r="I10" s="1">
-        <v>36.4</v>
-      </c>
-      <c r="J10">
-        <v>1.51</v>
-      </c>
-      <c r="K10" s="1">
-        <v>39.26</v>
-      </c>
-      <c r="L10" t="s">
-        <v>60</v>
-      </c>
-      <c r="M10">
+      <c r="F11">
+        <v>43.142</v>
+      </c>
+      <c r="G11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11">
+        <v>1.629</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1.689</v>
+      </c>
+      <c r="J11">
+        <v>72.866838</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1.76</v>
+      </c>
+      <c r="L11" s="1">
+        <v>75.92992</v>
+      </c>
+      <c r="M11" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11">
         <v>0</v>
       </c>
-      <c r="N10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11">
-        <v>43.14</v>
-      </c>
-      <c r="G11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11">
-        <v>1.69</v>
-      </c>
-      <c r="I11" s="1">
-        <v>72.91</v>
-      </c>
-      <c r="J11">
-        <v>1.76</v>
-      </c>
-      <c r="K11" s="1">
-        <v>75.93000000000001</v>
-      </c>
-      <c r="L11" t="s">
-        <v>61</v>
-      </c>
-      <c r="M11">
+      <c r="O11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12">
+        <v>30.309</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12">
+        <v>1.369</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1.399</v>
+      </c>
+      <c r="J12">
+        <v>42.402291</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="L12" s="1">
+        <v>45.16041</v>
+      </c>
+      <c r="M12" t="s">
+        <v>63</v>
+      </c>
+      <c r="N12">
         <v>0</v>
       </c>
-      <c r="N11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12">
-        <v>30.31</v>
-      </c>
-      <c r="G12" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12">
-        <v>1.4</v>
-      </c>
-      <c r="I12" s="1">
-        <v>42.43</v>
-      </c>
-      <c r="J12">
-        <v>1.49</v>
-      </c>
-      <c r="K12" s="1">
-        <v>45.16</v>
-      </c>
-      <c r="L12" t="s">
-        <v>62</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F13">
         <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H13">
-        <v>1.42</v>
+        <v>1.389</v>
       </c>
       <c r="I13" s="1">
-        <v>49.7</v>
+        <v>1.419</v>
       </c>
       <c r="J13">
+        <v>49.665</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.55</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>54.25</v>
       </c>
-      <c r="L13" t="s">
-        <v>63</v>
-      </c>
-      <c r="M13">
+      <c r="M13" t="s">
+        <v>64</v>
+      </c>
+      <c r="N13">
         <v>0</v>
       </c>
-      <c r="N13" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14">
+        <v>29.348</v>
+      </c>
+      <c r="G14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14">
+        <v>1.389</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1.419</v>
+      </c>
+      <c r="J14">
+        <v>41.644812</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L14" s="1">
+        <v>45.4894</v>
+      </c>
+      <c r="M14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15">
+        <v>43.462</v>
+      </c>
+      <c r="G15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15">
+        <v>1.648</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1.728</v>
+      </c>
+      <c r="J15">
+        <v>75.10233599999999</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1.99</v>
+      </c>
+      <c r="L15" s="1">
+        <v>86.48938</v>
+      </c>
+      <c r="M15" t="s">
+        <v>66</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16">
+        <v>25.578</v>
+      </c>
+      <c r="G16" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16">
+        <v>1.401</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1.431</v>
+      </c>
+      <c r="J16">
+        <v>36.602118</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L16" s="1">
+        <v>39.39012</v>
+      </c>
+      <c r="M16" t="s">
+        <v>67</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17">
+        <v>31.253</v>
+      </c>
+      <c r="G17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17">
+        <v>1.401</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1.431</v>
+      </c>
+      <c r="J17">
+        <v>44.723043</v>
+      </c>
+      <c r="K17" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="L17" s="1">
+        <v>49.37974</v>
+      </c>
+      <c r="M17" t="s">
+        <v>68</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18">
+        <v>15.019</v>
+      </c>
+      <c r="G18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18">
+        <v>1.401</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1.431</v>
+      </c>
+      <c r="J18">
+        <v>21.492189</v>
+      </c>
+      <c r="K18" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L18" s="1">
+        <v>23.42964</v>
+      </c>
+      <c r="M18" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18">
+        <v>73500</v>
+      </c>
+      <c r="O18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14">
-        <v>29.35</v>
-      </c>
-      <c r="G14" t="s">
-        <v>51</v>
-      </c>
-      <c r="H14">
-        <v>1.42</v>
-      </c>
-      <c r="I14" s="1">
-        <v>41.68</v>
-      </c>
-      <c r="J14">
-        <v>1.55</v>
-      </c>
-      <c r="K14" s="1">
-        <v>45.49</v>
-      </c>
-      <c r="L14" t="s">
-        <v>64</v>
-      </c>
-      <c r="M14">
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19">
+        <v>30.173</v>
+      </c>
+      <c r="G19" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19">
+        <v>1.449</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1.479</v>
+      </c>
+      <c r="J19">
+        <v>44.625867</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L19" s="1">
+        <v>47.06988</v>
+      </c>
+      <c r="M19" t="s">
+        <v>69</v>
+      </c>
+      <c r="N19">
         <v>0</v>
       </c>
-      <c r="N14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15">
-        <v>43.46</v>
-      </c>
-      <c r="G15" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15">
-        <v>1.73</v>
-      </c>
-      <c r="I15" s="1">
-        <v>75.19</v>
-      </c>
-      <c r="J15">
-        <v>1.99</v>
-      </c>
-      <c r="K15" s="1">
-        <v>86.48999999999999</v>
-      </c>
-      <c r="L15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16">
-        <v>25.58</v>
-      </c>
-      <c r="G16" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16">
-        <v>1.43</v>
-      </c>
-      <c r="I16" s="1">
-        <v>36.58</v>
-      </c>
-      <c r="J16">
-        <v>1.54</v>
-      </c>
-      <c r="K16" s="1">
-        <v>39.39</v>
-      </c>
-      <c r="L16" t="s">
-        <v>66</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17">
-        <v>31.25</v>
-      </c>
-      <c r="G17" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17">
-        <v>1.43</v>
-      </c>
-      <c r="I17" s="1">
-        <v>44.69</v>
-      </c>
-      <c r="J17">
-        <v>1.58</v>
-      </c>
-      <c r="K17" s="1">
-        <v>49.38</v>
-      </c>
-      <c r="L17" t="s">
-        <v>67</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18">
-        <v>15.02</v>
-      </c>
-      <c r="G18" t="s">
-        <v>51</v>
-      </c>
-      <c r="H18">
-        <v>1.43</v>
-      </c>
-      <c r="I18" s="1">
-        <v>21.48</v>
-      </c>
-      <c r="J18">
-        <v>1.56</v>
-      </c>
-      <c r="K18" s="1">
-        <v>23.43</v>
-      </c>
-      <c r="L18" t="s">
-        <v>54</v>
-      </c>
-      <c r="M18">
-        <v>73500</v>
-      </c>
-      <c r="N18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19">
-        <v>30.17</v>
-      </c>
-      <c r="G19" t="s">
-        <v>51</v>
-      </c>
-      <c r="H19">
-        <v>1.48</v>
-      </c>
-      <c r="I19" s="1">
-        <v>44.65</v>
-      </c>
-      <c r="J19">
-        <v>1.56</v>
-      </c>
-      <c r="K19" s="1">
-        <v>47.07</v>
-      </c>
-      <c r="L19" t="s">
-        <v>68</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O19" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1557,49 +1617,49 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:15">
       <c r="A23" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B24" s="6">
-        <v>397.33</v>
+        <v>397.328</v>
       </c>
       <c r="C24" s="6">
         <v>14</v>
       </c>
       <c r="D24" s="7">
-        <v>1.410339</v>
+        <v>1.409705</v>
       </c>
       <c r="E24" s="6">
-        <v>560.37</v>
+        <v>560.12</v>
       </c>
       <c r="F24" s="6">
         <v>606.45</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:15">
       <c r="A25" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B25" s="6">
         <v>61.05</v>
@@ -1608,68 +1668,68 @@
         <v>2</v>
       </c>
       <c r="D25" s="7">
-        <v>1.715643</v>
+        <v>1.713884</v>
       </c>
       <c r="E25" s="6">
-        <v>104.74</v>
+        <v>104.63</v>
       </c>
       <c r="F25" s="6">
         <v>118.5</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:15">
       <c r="A26" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B26" s="6">
-        <v>52.13</v>
+        <v>52.129</v>
       </c>
       <c r="C26" s="6">
         <v>1</v>
       </c>
       <c r="D26" s="7">
-        <v>1.440054</v>
+        <v>1.436</v>
       </c>
       <c r="E26" s="6">
-        <v>75.06999999999999</v>
+        <v>74.86</v>
       </c>
       <c r="F26" s="6">
         <v>80.8</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:15">
       <c r="A27" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B27" s="6">
-        <v>43.14</v>
+        <v>43.142</v>
       </c>
       <c r="C27" s="6">
         <v>1</v>
       </c>
       <c r="D27" s="7">
-        <v>1.690079</v>
+        <v>1.689</v>
       </c>
       <c r="E27" s="6">
-        <v>72.91</v>
+        <v>72.87</v>
       </c>
       <c r="F27" s="6">
         <v>75.93000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:15">
       <c r="A28" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B28" s="9">
-        <v>553.65</v>
+        <v>553.649</v>
       </c>
       <c r="C28" s="9">
         <v>18</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="9">
-        <v>813.09</v>
+        <v>812.48</v>
       </c>
       <c r="F28" s="9">
         <v>881.6799999999999</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 1/СКИМПРОТ ООД % ГРУПА 1.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СКИМПРОТ ООД % ГРУПА 1/СКИМПРОТ ООД % ГРУПА 1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="93">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -303,8 +300,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -397,10 +394,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -695,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -708,13 +705,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -757,859 +754,802 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F2">
         <v>26.921</v>
       </c>
       <c r="G2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2">
+        <v>1.389</v>
+      </c>
+      <c r="I2" s="1">
+        <v>37.393</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>40.651</v>
+      </c>
+      <c r="L2" t="s">
         <v>52</v>
       </c>
-      <c r="H2">
-        <v>1.359</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.389</v>
-      </c>
-      <c r="J2">
-        <v>37.393269</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>40.65071</v>
-      </c>
-      <c r="M2" t="s">
-        <v>53</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F3">
         <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H3">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I3" s="1">
-        <v>1.389</v>
+        <v>50.004</v>
       </c>
       <c r="J3">
-        <v>50.004</v>
+        <v>1.51</v>
       </c>
       <c r="K3" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L3" s="1">
         <v>54.36</v>
       </c>
-      <c r="M3" t="s">
-        <v>54</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="L3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F4">
         <v>21.553</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H4">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I4" s="1">
-        <v>1.389</v>
+        <v>29.937</v>
       </c>
       <c r="J4">
-        <v>29.937117</v>
+        <v>1.5</v>
       </c>
       <c r="K4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L4" s="1">
-        <v>32.3295</v>
-      </c>
-      <c r="M4" t="s">
-        <v>55</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>32.33</v>
+      </c>
+      <c r="L4" t="s">
+        <v>54</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F5">
         <v>22.789</v>
       </c>
       <c r="G5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H5">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I5" s="1">
-        <v>1.389</v>
+        <v>31.654</v>
       </c>
       <c r="J5">
-        <v>31.653921</v>
+        <v>1.52</v>
       </c>
       <c r="K5" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L5" s="1">
-        <v>34.63928</v>
-      </c>
-      <c r="M5" t="s">
-        <v>56</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>34.639</v>
+      </c>
+      <c r="L5" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F6">
         <v>52.129</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H6">
-        <v>1.406</v>
+        <v>1.436</v>
       </c>
       <c r="I6" s="1">
-        <v>1.436</v>
+        <v>74.857</v>
       </c>
       <c r="J6">
-        <v>74.85724399999999</v>
+        <v>1.55</v>
       </c>
       <c r="K6" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L6" s="1">
-        <v>80.79995</v>
-      </c>
-      <c r="M6" t="s">
-        <v>57</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>80.8</v>
+      </c>
+      <c r="L6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F7">
         <v>17.588</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H7">
-        <v>1.599</v>
+        <v>1.679</v>
       </c>
       <c r="I7" s="1">
-        <v>1.679</v>
+        <v>29.53</v>
       </c>
       <c r="J7">
-        <v>29.530252</v>
+        <v>1.82</v>
       </c>
       <c r="K7" s="1">
-        <v>1.82</v>
-      </c>
-      <c r="L7" s="1">
-        <v>32.01016</v>
-      </c>
-      <c r="M7" t="s">
-        <v>58</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>32.01</v>
+      </c>
+      <c r="L7" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F8">
         <v>46.148</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H8">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I8" s="1">
-        <v>1.389</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J8">
-        <v>64.09957199999999</v>
+        <v>1.49</v>
       </c>
       <c r="K8" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L8" s="1">
-        <v>68.76052</v>
-      </c>
-      <c r="M8" t="s">
-        <v>59</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>68.761</v>
+      </c>
+      <c r="L8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F9">
         <v>21.237</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H9">
-        <v>1.359</v>
+        <v>1.389</v>
       </c>
       <c r="I9" s="1">
-        <v>1.389</v>
+        <v>29.498</v>
       </c>
       <c r="J9">
-        <v>29.498193</v>
+        <v>1.52</v>
       </c>
       <c r="K9" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L9" s="1">
-        <v>32.28024</v>
-      </c>
-      <c r="M9" t="s">
-        <v>60</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>32.28</v>
+      </c>
+      <c r="L9" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F10">
         <v>26</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H10">
-        <v>1.369</v>
+        <v>1.399</v>
       </c>
       <c r="I10" s="1">
-        <v>1.399</v>
+        <v>36.374</v>
       </c>
       <c r="J10">
-        <v>36.374</v>
+        <v>1.51</v>
       </c>
       <c r="K10" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L10" s="1">
         <v>39.26</v>
       </c>
-      <c r="M10" t="s">
-        <v>61</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="L10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F11">
         <v>43.142</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H11">
-        <v>1.629</v>
+        <v>1.689</v>
       </c>
       <c r="I11" s="1">
-        <v>1.689</v>
+        <v>72.867</v>
       </c>
       <c r="J11">
-        <v>72.866838</v>
+        <v>1.76</v>
       </c>
       <c r="K11" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L11" s="1">
-        <v>75.92992</v>
-      </c>
-      <c r="M11" t="s">
-        <v>62</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>75.93000000000001</v>
+      </c>
+      <c r="L11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
         <v>47</v>
-      </c>
-      <c r="E12" t="s">
-        <v>48</v>
       </c>
       <c r="F12">
         <v>30.309</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H12">
-        <v>1.369</v>
+        <v>1.399</v>
       </c>
       <c r="I12" s="1">
-        <v>1.399</v>
+        <v>42.402</v>
       </c>
       <c r="J12">
-        <v>42.402291</v>
+        <v>1.49</v>
       </c>
       <c r="K12" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L12" s="1">
-        <v>45.16041</v>
-      </c>
-      <c r="M12" t="s">
-        <v>63</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>45.16</v>
+      </c>
+      <c r="L12" t="s">
+        <v>62</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F13">
         <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H13">
-        <v>1.389</v>
+        <v>1.419</v>
       </c>
       <c r="I13" s="1">
-        <v>1.419</v>
+        <v>49.665</v>
       </c>
       <c r="J13">
-        <v>49.665</v>
+        <v>1.55</v>
       </c>
       <c r="K13" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L13" s="1">
         <v>54.25</v>
       </c>
-      <c r="M13" t="s">
-        <v>64</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="L13" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F14">
         <v>29.348</v>
       </c>
       <c r="G14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H14">
-        <v>1.389</v>
+        <v>1.419</v>
       </c>
       <c r="I14" s="1">
-        <v>1.419</v>
+        <v>41.645</v>
       </c>
       <c r="J14">
-        <v>41.644812</v>
+        <v>1.55</v>
       </c>
       <c r="K14" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L14" s="1">
-        <v>45.4894</v>
-      </c>
-      <c r="M14" t="s">
-        <v>65</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>45.489</v>
+      </c>
+      <c r="L14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F15">
         <v>43.462</v>
       </c>
       <c r="G15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H15">
-        <v>1.648</v>
+        <v>1.728</v>
       </c>
       <c r="I15" s="1">
-        <v>1.728</v>
+        <v>75.102</v>
       </c>
       <c r="J15">
-        <v>75.10233599999999</v>
+        <v>1.99</v>
       </c>
       <c r="K15" s="1">
-        <v>1.99</v>
-      </c>
-      <c r="L15" s="1">
-        <v>86.48938</v>
-      </c>
-      <c r="M15" t="s">
-        <v>66</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>86.489</v>
+      </c>
+      <c r="L15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" t="s">
         <v>47</v>
-      </c>
-      <c r="E16" t="s">
-        <v>48</v>
       </c>
       <c r="F16">
         <v>25.578</v>
       </c>
       <c r="G16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H16">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I16" s="1">
-        <v>1.431</v>
+        <v>36.602</v>
       </c>
       <c r="J16">
-        <v>36.602118</v>
+        <v>1.54</v>
       </c>
       <c r="K16" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L16" s="1">
-        <v>39.39012</v>
-      </c>
-      <c r="M16" t="s">
-        <v>67</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>39.39</v>
+      </c>
+      <c r="L16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F17">
         <v>31.253</v>
       </c>
       <c r="G17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H17">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I17" s="1">
-        <v>1.431</v>
+        <v>44.723</v>
       </c>
       <c r="J17">
-        <v>44.723043</v>
+        <v>1.58</v>
       </c>
       <c r="K17" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="L17" s="1">
-        <v>49.37974</v>
-      </c>
-      <c r="M17" t="s">
-        <v>68</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>49.38</v>
+      </c>
+      <c r="L17" t="s">
+        <v>67</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18">
         <v>15.019</v>
       </c>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H18">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I18" s="1">
-        <v>1.431</v>
+        <v>21.492</v>
       </c>
       <c r="J18">
-        <v>21.492189</v>
+        <v>1.56</v>
       </c>
       <c r="K18" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L18" s="1">
-        <v>23.42964</v>
-      </c>
-      <c r="M18" t="s">
-        <v>55</v>
-      </c>
-      <c r="N18">
+        <v>23.43</v>
+      </c>
+      <c r="L18" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18">
         <v>73500</v>
       </c>
-      <c r="O18" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="N18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
         <v>27</v>
       </c>
-      <c r="B19" t="s">
-        <v>28</v>
-      </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F19">
         <v>30.173</v>
       </c>
       <c r="G19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H19">
-        <v>1.449</v>
+        <v>1.479</v>
       </c>
       <c r="I19" s="1">
-        <v>1.479</v>
+        <v>44.626</v>
       </c>
       <c r="J19">
-        <v>44.625867</v>
+        <v>1.56</v>
       </c>
       <c r="K19" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L19" s="1">
-        <v>47.06988</v>
-      </c>
-      <c r="M19" t="s">
-        <v>69</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
+        <v>47.07</v>
+      </c>
+      <c r="L19" t="s">
+        <v>68</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="3" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1617,109 +1557,109 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:14">
       <c r="A23" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>92</v>
-      </c>
       <c r="E23" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B24" s="6">
         <v>397.328</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="7">
         <v>14</v>
       </c>
       <c r="D24" s="7">
-        <v>1.409705</v>
-      </c>
-      <c r="E24" s="6">
-        <v>560.12</v>
-      </c>
-      <c r="F24" s="6">
+        <v>1.41</v>
+      </c>
+      <c r="E24" s="7">
+        <v>560.115</v>
+      </c>
+      <c r="F24" s="7">
         <v>606.45</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:14">
       <c r="A25" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B25" s="6">
         <v>61.05</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="7">
         <v>2</v>
       </c>
       <c r="D25" s="7">
-        <v>1.713884</v>
-      </c>
-      <c r="E25" s="6">
-        <v>104.63</v>
-      </c>
-      <c r="F25" s="6">
-        <v>118.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>1.714</v>
+      </c>
+      <c r="E25" s="7">
+        <v>104.632</v>
+      </c>
+      <c r="F25" s="7">
+        <v>118.499</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" s="6">
         <v>52.129</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="7">
         <v>1</v>
       </c>
       <c r="D26" s="7">
         <v>1.436</v>
       </c>
-      <c r="E26" s="6">
-        <v>74.86</v>
-      </c>
-      <c r="F26" s="6">
+      <c r="E26" s="7">
+        <v>74.857</v>
+      </c>
+      <c r="F26" s="7">
         <v>80.8</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:14">
       <c r="A27" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="6">
         <v>43.142</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="7">
         <v>1</v>
       </c>
       <c r="D27" s="7">
         <v>1.689</v>
       </c>
-      <c r="E27" s="6">
-        <v>72.87</v>
-      </c>
-      <c r="F27" s="6">
+      <c r="E27" s="7">
+        <v>72.867</v>
+      </c>
+      <c r="F27" s="7">
         <v>75.93000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:14">
       <c r="A28" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B28" s="9">
         <v>553.649</v>
@@ -1729,10 +1669,10 @@
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="9">
-        <v>812.48</v>
+        <v>812.471</v>
       </c>
       <c r="F28" s="9">
-        <v>881.6799999999999</v>
+        <v>881.679</v>
       </c>
     </row>
   </sheetData>
